--- a/SAEN PEÑA/Junio/SAENZ_EXPENSAS-JUNIO.xlsx
+++ b/SAEN PEÑA/Junio/SAENZ_EXPENSAS-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EA041A-3439-4EB3-A2C8-97576CB6F57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8A09E2-A19C-4C4D-A628-6B2010DA8318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
   <si>
     <t>UF</t>
   </si>
@@ -234,19 +234,22 @@
     <t>Honorarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Compra de picaporte </t>
-  </si>
-  <si>
     <t>Prevision</t>
   </si>
   <si>
     <t>Liquidacion mes de JUNIO</t>
   </si>
   <si>
-    <t>EL EDESUR DE JUNIO LO PAGAMOS SIN QUERES EN JUNIO -  ES DE 31541,58</t>
-  </si>
-  <si>
     <t xml:space="preserve">Período JUNIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra de membrana 20kg  </t>
+  </si>
+  <si>
+    <t>Camion Villar -  Destapaciones</t>
+  </si>
+  <si>
+    <t>SAC</t>
   </si>
 </sst>
 </file>
@@ -259,7 +262,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,15 +363,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,12 +413,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1062,7 +1052,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1308,9 +1298,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1678,7 +1665,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1689,12 +1676,12 @@
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1702,27 +1689,27 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1730,11 +1717,11 @@
       <c r="C7" s="62"/>
       <c r="D7" s="62"/>
       <c r="E7" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="103"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1742,12 +1729,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="106" t="s">
         <v>12</v>
       </c>
@@ -1759,14 +1746,14 @@
       </c>
       <c r="F11" s="112"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="104" t="s">
         <v>61</v>
       </c>
       <c r="B12" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="131">
+      <c r="C12" s="111">
         <v>32362.99</v>
       </c>
       <c r="D12" s="5"/>
@@ -1774,10 +1761,10 @@
         <v>48</v>
       </c>
       <c r="F12" s="50">
-        <v>487962.0693284091</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>437075.38143240911</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="102" t="s">
         <v>66</v>
       </c>
@@ -1793,17 +1780,17 @@
       </c>
       <c r="F13" s="52">
         <f>'prorrateo '!F11</f>
-        <v>135915.367104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>327812.56501932401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="104" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="133">
+      <c r="C14" s="111">
         <v>31541.58</v>
       </c>
       <c r="D14" s="5"/>
@@ -1811,14 +1798,11 @@
         <v>22</v>
       </c>
       <c r="F14" s="52">
-        <f>-(C34)</f>
-        <v>-192906.155</v>
-      </c>
-      <c r="G14" s="132" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <f>-(C36)</f>
+        <v>-396675.17749999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="102" t="s">
         <v>21</v>
       </c>
@@ -1831,7 +1815,7 @@
       <c r="E15" s="51"/>
       <c r="F15" s="52"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="107"/>
       <c r="B16" s="108"/>
       <c r="C16" s="82">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="F16" s="54">
         <f>SUM(F12:F15)</f>
-        <v>430971.28143240907</v>
+        <v>368212.76895173313</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1861,7 +1845,7 @@
         <v>42</v>
       </c>
       <c r="B18" s="110" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" s="75">
         <f xml:space="preserve"> 51328.1+51328.1*5%</f>
@@ -1873,180 +1857,197 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="102" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B19" s="110"/>
-      <c r="C19" s="111">
-        <v>13060.08</v>
+      <c r="C19" s="75">
+        <f>C18/2</f>
+        <v>26947.252499999999</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="102" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
+      <c r="C20" s="75">
+        <f>80000+50000</f>
+        <v>130000</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="107"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="82">
-        <f>SUM(C17:C20)</f>
-        <v>66954.584999999992</v>
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="102" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="110"/>
+      <c r="C21" s="111">
+        <f>119763.7/2</f>
+        <v>59881.85</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="6"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42">
-        <f>+C21+C16</f>
-        <v>192906.155</v>
-      </c>
+      <c r="A22" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="110"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="107"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="82">
+        <f>SUM(C17:C22)</f>
+        <v>270723.60749999998</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42">
+        <f>+C23+C16</f>
+        <v>396675.17749999999</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="B25" s="77"/>
+      <c r="C25" s="78"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="47"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="46">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6"/>
-    </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="46">
-        <v>0</v>
-      </c>
+      <c r="A27" s="37"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="47"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="76"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="45"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="46">
+        <v>0</v>
+      </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="81"/>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="55"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="46">
+        <v>0</v>
+      </c>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="73"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="76">
-        <v>0</v>
-      </c>
+      <c r="B30" s="74"/>
+      <c r="C30" s="76"/>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="73"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="81"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="73"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="76">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="58"/>
-      <c r="C31" s="59">
-        <f>SUM(C26:C30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B33" s="58"/>
+      <c r="C33" s="59">
+        <f>SUM(C28:C32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="46">
-        <f>C22-C20</f>
-        <v>192906.155</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="C34" s="46">
+        <f>C24-C22</f>
+        <v>396675.17749999999</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="72">
-        <f>+C22</f>
-        <v>192906.155</v>
-      </c>
-      <c r="E33" s="105"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="s">
+      <c r="C35" s="72">
+        <f>+C24</f>
+        <v>396675.17749999999</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="59">
-        <f>C32</f>
-        <v>192906.155</v>
-      </c>
-      <c r="E34" s="16"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="59">
+        <f>C34</f>
+        <v>396675.17749999999</v>
+      </c>
+      <c r="E36" s="16"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="6"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="19"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="20"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="16"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="16"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
+      <c r="A57" s="19"/>
       <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
+      <c r="C57" s="20"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
@@ -2072,6 +2073,16 @@
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2128,7 +2139,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="65">
-        <v>186802.05499999999</v>
+        <v>396675.17749999999</v>
       </c>
       <c r="L1" s="27"/>
     </row>
@@ -2233,11 +2244,11 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>30828.688128000002</v>
+        <v>28244.470716</v>
       </c>
       <c r="F5" s="75">
         <f t="shared" ref="F5:F8" si="0">E5</f>
-        <v>30828.688128000002</v>
+        <v>28244.470716</v>
       </c>
       <c r="G5" s="61">
         <f>E5-F5</f>
@@ -2252,7 +2263,7 @@
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>28244.470716</v>
+        <v>59977.286838</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2260,7 +2271,7 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>28244.470716</v>
+        <v>59977.286838</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2277,23 +2288,26 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>31990.880736000003</v>
-      </c>
-      <c r="F6" s="75"/>
+        <v>63987.357147324001</v>
+      </c>
+      <c r="F6" s="75">
+        <f>E6</f>
+        <v>63987.357147324001</v>
+      </c>
       <c r="G6" s="61">
         <f t="shared" ref="G6:G8" si="1">E6-F6</f>
-        <v>31990.880736000003</v>
+        <v>0</v>
       </c>
       <c r="H6" s="64">
         <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>2687.2339818240002</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>29309.242429500002</v>
+        <v>62238.335349750007</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2301,7 +2315,7 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>63987.357147324001</v>
+        <v>62238.335349750007</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2318,26 +2332,23 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>32255.942208</v>
-      </c>
-      <c r="F7" s="75">
-        <f t="shared" si="0"/>
-        <v>32255.942208</v>
-      </c>
+        <v>29552.085101000001</v>
+      </c>
+      <c r="F7" s="75"/>
       <c r="G7" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>29552.085101000001</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2482.3751484840004</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>29552.085101000001</v>
+        <v>62754.013080500001</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2345,7 +2356,7 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>29552.085101000001</v>
+        <v>94788.473329984001</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2362,26 +2373,23 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>40370.901120000002</v>
-      </c>
-      <c r="F8" s="75">
-        <f t="shared" si="0"/>
-        <v>40370.901120000002</v>
-      </c>
+        <v>36986.80689</v>
+      </c>
+      <c r="F8" s="75"/>
       <c r="G8" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36986.80689</v>
       </c>
       <c r="H8" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3106.8917787600003</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>36986.80689</v>
+        <v>78541.685144999996</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2389,7 +2397,7 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>36986.80689</v>
+        <v>118635.38381376001</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2406,11 +2414,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>32459.835648</v>
+        <v>29738.887156000001</v>
       </c>
       <c r="F9" s="75">
         <f>E9</f>
-        <v>32459.835648</v>
+        <v>29738.887156000001</v>
       </c>
       <c r="G9" s="61">
         <f>E9-F9</f>
@@ -2425,7 +2433,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>29738.887156000001</v>
+        <v>63150.688258000002</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2433,7 +2441,7 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="3"/>
-        <v>29738.887156000001</v>
+        <v>63150.688258000002</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2450,23 +2458,26 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>104233.64702196</v>
-      </c>
-      <c r="F10" s="75"/>
+        <v>145959.83607930463</v>
+      </c>
+      <c r="F10" s="75">
+        <f>145960+'detalle y gastos'!C21</f>
+        <v>205841.85</v>
+      </c>
       <c r="G10" s="61">
         <f>E10-F10</f>
-        <v>104233.64702196</v>
+        <v>-59882.013920695375</v>
       </c>
       <c r="H10" s="64">
         <f t="shared" si="2"/>
-        <v>8755.6263498446406</v>
+        <v>0</v>
       </c>
       <c r="I10" s="15">
         <v>0</v>
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>32970.562707499994</v>
+        <v>70013.16882875</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2474,7 +2485,7 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>145959.83607930463</v>
+        <v>10131.154908054625</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2489,19 +2500,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>272139.89486195997</v>
+        <v>334469.44308962865</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>135915.367104</v>
+        <v>327812.56501932401</v>
       </c>
       <c r="G11" s="43">
         <f>SUM(G5:G10)</f>
-        <v>136224.52775795999</v>
+        <v>6656.8780703046214</v>
       </c>
       <c r="H11" s="43">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>11442.86033166864</v>
+        <v>5589.2669272440007</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2509,7 +2520,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>186802.05499999999</v>
+        <v>396675.17749999999</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2517,7 +2528,7 @@
       </c>
       <c r="L11" s="43">
         <f>SUM(L5:L10)</f>
-        <v>334469.44308962865</v>
+        <v>408921.32249754865</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
